--- a/History/History.xlsx
+++ b/History/History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,7 +439,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Txn_Type</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -531,6 +531,44 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>Location: [Connect Geolocation API here]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>11:08:25</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>sunny</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Shopping</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>4333</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4333</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Vijayawada, Andhra Pradesh, IN</t>
         </is>
       </c>
     </row>

--- a/History/History.xlsx
+++ b/History/History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,26 +457,36 @@
           <t>Location</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Session_Time</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Txn_Duration_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12:31:13</t>
+          <t>11:24:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sunny</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Shopping</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -485,31 +495,39 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>300</v>
+        <v>5000</v>
       </c>
       <c r="G2" t="n">
-        <v>300</v>
+        <v>5000</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Location: [Connect Geolocation API here]</t>
-        </is>
+          <t>Hyderabad, Telangana, IN</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>29.61s</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>19.39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:31:55</t>
+          <t>11:24:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sunny</t>
+          <t>swiggy</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -523,53 +541,23 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5000</v>
+        <v>300</v>
       </c>
       <c r="G3" t="n">
-        <v>5000</v>
+        <v>300</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Location: [Connect Geolocation API here]</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>11:08:25</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>sunny</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Shopping</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>UPI</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>4333</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4333</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Vijayawada, Andhra Pradesh, IN</t>
-        </is>
+          <t>Hyderabad, Telangana, IN</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>42.91s</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>22.69</v>
       </c>
     </row>
   </sheetData>
